--- a/word/csvfile/协议模板.xlsx
+++ b/word/csvfile/协议模板.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11214"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuanyuqing/Documents/code/schoolProject/word/csvfile/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codes\protocol-conversion-tool\word\csvfile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3991EE75-38BB-1E41-BAF5-0BD48E63BCA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EBA2223-B1AA-4FE1-AC0C-00835BD3742F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="23260" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="协议模板（公开）.docx" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -28,6 +29,9 @@
     <t>信源系统码</t>
   </si>
   <si>
+    <t>信源机器码</t>
+  </si>
+  <si>
     <t>信宿系统码</t>
   </si>
   <si>
@@ -65,17 +69,13 @@
   </si>
   <si>
     <t>备注</t>
-  </si>
-  <si>
-    <t>信源机器码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -86,10 +86,8 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -99,18 +97,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -140,12 +132,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -166,9 +155,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -206,7 +195,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -240,7 +229,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -275,10 +263,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -453,68 +440,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <cols>
-    <col min="2" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.5" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/word/csvfile/协议模板.xlsx
+++ b/word/csvfile/协议模板.xlsx
@@ -1,105 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codes\protocol-conversion-tool\word\csvfile\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EBA2223-B1AA-4FE1-AC0C-00835BD3742F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="协议模板（公开）.docx" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="协议模板（公开）.docx" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>信源系统码</t>
-  </si>
-  <si>
-    <t>信源机器码</t>
-  </si>
-  <si>
-    <t>信宿系统码</t>
-  </si>
-  <si>
-    <t>信宿机器码</t>
-  </si>
-  <si>
-    <t>子地址或消息地址</t>
-  </si>
-  <si>
-    <t>数据段长度（总线为字，其他为字节）</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>内容</t>
-  </si>
-  <si>
-    <t>子内容</t>
-  </si>
-  <si>
-    <t>类型（bit）</t>
-  </si>
-  <si>
-    <t>转换类型</t>
-  </si>
-  <si>
-    <t>判读公式（暂不设计）</t>
-  </si>
-  <si>
-    <t>转换公式（变量必须为x）</t>
-  </si>
-  <si>
-    <t>单位</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -133,24 +74,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -438,63 +438,98 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>信源系统码</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>信源机器码</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>信宿系统码</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>信宿机器码</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>子地址</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>数据段长度</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>子内容</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>类型（bit）</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>转换类型</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>判读公式</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>转换公式</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/word/csvfile/协议模板.xlsx
+++ b/word/csvfile/协议模板.xlsx
@@ -1,46 +1,106 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuanyuqing/Documents/code/schoolProject/word/csvfile/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F144CE33-8C1A-F74D-97B9-C064D3E94AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="25820" windowHeight="14620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="协议模板（公开）.docx" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="协议模板（公开）.docx" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>信源系统码</t>
+  </si>
+  <si>
+    <t>信源机器码</t>
+  </si>
+  <si>
+    <t>信宿系统码</t>
+  </si>
+  <si>
+    <t>信宿机器码</t>
+  </si>
+  <si>
+    <t>子地址</t>
+  </si>
+  <si>
+    <t>数据段长度</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>内容</t>
+  </si>
+  <si>
+    <t>子内容</t>
+  </si>
+  <si>
+    <t>类型（bit）</t>
+  </si>
+  <si>
+    <t>转换类型</t>
+  </si>
+  <si>
+    <t>判读公式</t>
+  </si>
+  <si>
+    <t>单位</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>转换公式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <b val="1"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -74,83 +134,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -438,98 +439,63 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>信源系统码</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>信源机器码</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>信宿系统码</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>信宿机器码</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>子地址</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>数据段长度</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>子内容</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>类型（bit）</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>转换类型</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>判读公式</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>转换公式</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>单位</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
+    <row r="1" spans="1:16">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>